--- a/Design_files/BOM_master.xlsx
+++ b/Design_files/BOM_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Princeton Dropbox\Lin Yubin\KENNEL\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yubinlin/Documents/CohenLab/GIT/SCHEPHERD_CODE_PUBLIC/Design_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CEECE2-3EE8-4B32-AD19-4C468190D56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5467F13-1670-7743-B3B7-9EBAF7F91805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="4260" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="18100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAD_file" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Name</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Agar acrylic mold dxf</t>
   </si>
   <si>
-    <t>Electrode deposition</t>
-  </si>
-  <si>
     <t>Incubator lid spacer for PCB</t>
   </si>
   <si>
@@ -199,6 +196,12 @@
   </si>
   <si>
     <t>Soldering iron</t>
+  </si>
+  <si>
+    <t>Motherboard</t>
+  </si>
+  <si>
+    <t>Electrode_lid</t>
   </si>
 </sst>
 </file>
@@ -517,13 +520,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,82 +534,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -619,31 +622,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A274075A-A70F-404F-8BB1-E40F18F97278}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="48.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -653,17 +656,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6721BC34-C750-40DD-AFEF-06FA70E1F67A}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -674,177 +682,177 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89DA596-4026-48FC-8F2D-ABECD3917435}">
   <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.5703125" customWidth="1"/>
+    <col min="1" max="2" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
